--- a/artfynd/A 73093-2021 artfynd.xlsx
+++ b/artfynd/A 73093-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73093-2021 artfynd.xlsx
+++ b/artfynd/A 73093-2021 artfynd.xlsx
@@ -1511,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120977601</v>
+        <v>120977598</v>
       </c>
       <c r="B9" t="n">
-        <v>98106</v>
+        <v>105267</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,44 +1527,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223619</v>
+        <v>221423</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
+          <t>Södra Råda, vid Messmyrarnas V-ände, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713754</v>
+        <v>713767</v>
       </c>
       <c r="R9" t="n">
-        <v>6645972</v>
+        <v>6646004</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1609,17 +1603,13 @@
           <t>20:10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ett stort ex i blom.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1646,7 +1636,7 @@
         <v>120977602</v>
       </c>
       <c r="B10" t="n">
-        <v>98050</v>
+        <v>98060</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1761,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120977598</v>
+        <v>120977600</v>
       </c>
       <c r="B11" t="n">
-        <v>105257</v>
+        <v>57779</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,45 +1763,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221423</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Råda, vid Messmyrarnas V-ände, Upl</t>
+          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713767</v>
+        <v>713754</v>
       </c>
       <c r="R11" t="n">
-        <v>6646004</v>
+        <v>6645972</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1859,7 +1857,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1883,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120977600</v>
+        <v>120977601</v>
       </c>
       <c r="B12" t="n">
-        <v>57776</v>
+        <v>98116</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,40 +1892,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>223619</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
@@ -1941,7 +1936,7 @@
         <v>6645972</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1981,6 +1976,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>20:10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett stort ex i blom.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 73093-2021 artfynd.xlsx
+++ b/artfynd/A 73093-2021 artfynd.xlsx
@@ -1511,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120977598</v>
+        <v>120977601</v>
       </c>
       <c r="B9" t="n">
-        <v>105267</v>
+        <v>98116</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,38 +1527,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221423</v>
+        <v>223619</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Råda, vid Messmyrarnas V-ände, Upl</t>
+          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713767</v>
+        <v>713754</v>
       </c>
       <c r="R9" t="n">
-        <v>6646004</v>
+        <v>6645972</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1603,13 +1609,17 @@
           <t>20:10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ett stort ex i blom.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1751,10 +1761,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120977600</v>
+        <v>120977598</v>
       </c>
       <c r="B11" t="n">
-        <v>57779</v>
+        <v>105267</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,53 +1773,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>221423</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
+          <t>Södra Råda, vid Messmyrarnas V-ände, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713754</v>
+        <v>713767</v>
       </c>
       <c r="R11" t="n">
-        <v>6645972</v>
+        <v>6646004</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1857,6 +1859,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1880,10 +1883,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120977601</v>
+        <v>120977600</v>
       </c>
       <c r="B12" t="n">
-        <v>98116</v>
+        <v>57779</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1892,38 +1895,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223619</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
@@ -1936,7 +1941,7 @@
         <v>6645972</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1976,11 +1981,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>20:10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ett stort ex i blom.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 73093-2021 artfynd.xlsx
+++ b/artfynd/A 73093-2021 artfynd.xlsx
@@ -1511,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120977601</v>
+        <v>120977598</v>
       </c>
       <c r="B9" t="n">
-        <v>98116</v>
+        <v>105280</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,44 +1527,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223619</v>
+        <v>221423</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
+          <t>Södra Råda, vid Messmyrarnas V-ände, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>713754</v>
+        <v>713767</v>
       </c>
       <c r="R9" t="n">
-        <v>6645972</v>
+        <v>6646004</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1609,17 +1603,13 @@
           <t>20:10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ett stort ex i blom.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1646,7 +1636,7 @@
         <v>120977602</v>
       </c>
       <c r="B10" t="n">
-        <v>98060</v>
+        <v>98073</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1761,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120977598</v>
+        <v>120977600</v>
       </c>
       <c r="B11" t="n">
-        <v>105267</v>
+        <v>57779</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,45 +1763,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221423</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Råda, vid Messmyrarnas V-ände, Upl</t>
+          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713767</v>
+        <v>713754</v>
       </c>
       <c r="R11" t="n">
-        <v>6646004</v>
+        <v>6645972</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1859,7 +1857,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1883,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120977600</v>
+        <v>120977601</v>
       </c>
       <c r="B12" t="n">
-        <v>57779</v>
+        <v>98129</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,40 +1892,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>223619</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
@@ -1941,7 +1936,7 @@
         <v>6645972</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1981,6 +1976,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>20:10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett stort ex i blom.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 73093-2021 artfynd.xlsx
+++ b/artfynd/A 73093-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5039492</v>
+        <v>6760838</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SÖDER LISSKÄRRET (11J9d07), Upl</t>
+          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713765.1690587909</v>
+        <v>713747</v>
       </c>
       <c r="R2" t="n">
-        <v>6645979.3647141</v>
+        <v>6645996</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1994-04-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1994-04-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>110993071 / HEPA NOB / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
+          <t>Endast blommande stjälkar räknade.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,31 +774,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Eklund</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens naturvärdesobjekt</t>
+          <t>Floraväkteri AB-län</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94037081</v>
+        <v>6762359</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,32 +818,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Messmyrarnas SV-ände, Upl</t>
+          <t>SÖDER LISSKÄRRET (11J9d07), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713752.819891345</v>
+        <v>713765</v>
       </c>
       <c r="R3" t="n">
-        <v>6646001.28157085</v>
+        <v>6645979</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,22 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>1994-04-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:43</t>
+          <t>1994-04-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>110993071 / CYPR CAL / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,27 +880,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Stefan Eklund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6760838</v>
+        <v>94037246</v>
       </c>
       <c r="B4" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,46 +907,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
+          <t>Messmyrarna, skogsbilväg V om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713747.0846395431</v>
+        <v>713786</v>
       </c>
       <c r="R4" t="n">
-        <v>6645995.92114509</v>
+        <v>6646053</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,27 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2006-06-26</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2006-06-26</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Endast blommande stjälkar räknade.</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,66 +1002,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri AB-län</t>
-        </is>
-      </c>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6762359</v>
+        <v>120977600</v>
       </c>
       <c r="B5" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SÖDER LISSKÄRRET (11J9d07), Upl</t>
+          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713765.1690587909</v>
+        <v>713754</v>
       </c>
       <c r="R5" t="n">
-        <v>6645979.3647141</v>
+        <v>6645972</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1123,27 +1091,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1994-04-06</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1994-04-06</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>110993071 / CYPR CAL / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,35 +1117,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gläntig örtrik blandskog med ädellövinslag, bryn mot gammalt hygge, nu bevuxet med yngre granar. Nyupptaget hygge i övriga riktningar.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Eklund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens naturvärdesobjekt</t>
-        </is>
-      </c>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113252976</v>
+        <v>94037254</v>
       </c>
       <c r="B6" t="n">
-        <v>106006</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,39 +1149,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219686</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
+          <t>Messmyrarna, skogsbilväg V om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713742</v>
+        <v>713786</v>
       </c>
       <c r="R6" t="n">
-        <v>6645991</v>
+        <v>6646053</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1249,22 +1214,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hörd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,15 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113252977</v>
+        <v>113252976</v>
       </c>
       <c r="B7" t="n">
-        <v>97629</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,20 +1272,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223609</v>
+        <v>219686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
@@ -1402,12 +1376,7 @@
         <v>113252978</v>
       </c>
       <c r="B8" t="n">
-        <v>97672</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,12 +1483,7 @@
         <v>120977598</v>
       </c>
       <c r="B9" t="n">
-        <v>105280</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,15 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120977602</v>
+        <v>94037081</v>
       </c>
       <c r="B10" t="n">
-        <v>98073</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,38 +1608,52 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223609</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
+          <t>Messmyrarnas SV-ände, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>713743</v>
+        <v>713753</v>
       </c>
       <c r="R10" t="n">
-        <v>6645990</v>
+        <v>6646001</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,22 +1677,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,11 +1703,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gläntig örtrik blandskog med ädellövinslag, bryn mot gammalt hygge, nu bevuxet med yngre granar. Nyupptaget hygge i övriga riktningar.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1751,62 +1719,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120977600</v>
+        <v>5039492</v>
       </c>
       <c r="B11" t="n">
-        <v>57779</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
+          <t>SÖDER LISSKÄRRET (11J9d07), Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>713754</v>
+        <v>713765</v>
       </c>
       <c r="R11" t="n">
-        <v>6645972</v>
+        <v>6645979</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1833,22 +1784,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>19:32</t>
+          <t>1994-04-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>20:10</t>
+          <t>1994-04-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>110993071 / HEPA NOB / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,36 +1805,30 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gläntig örtrik blandskog med ädellövinslag, bryn mot gammalt hygge, nu bevuxet med yngre granar. Nyupptaget hygge i övriga riktningar.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Stefan Eklund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120977601</v>
+        <v>113252977</v>
       </c>
       <c r="B12" t="n">
-        <v>98129</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99097</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,47 +1836,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223619</v>
+        <v>223609</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
+          <t>Epipactis helleborine subsp. helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>713754</v>
+        <v>713742</v>
       </c>
       <c r="R12" t="n">
-        <v>6645972</v>
+        <v>6645991</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1960,27 +1886,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ett stort ex i blom.</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,11 +1912,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gläntig örtrik blandskog med ädellövinslag, bryn mot gammalt hygge, nu bevuxet med yngre granar. Nyupptaget hygge i övriga riktningar.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2009,6 +1925,246 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120977602</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>713743</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6645990</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gläntig örtrik blandskog med ädellövinslag, bryn mot gammalt hygge, nu bevuxet med yngre granar. Nyupptaget hygge i övriga riktningar.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120977601</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223619</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ängsnattviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Södra Råda, vid Messmyrarnas SV-ände, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>713754</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6645972</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ett stort ex i blom.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gläntig örtrik blandskog med ädellövinslag, bryn mot gammalt hygge, nu bevuxet med yngre granar. Nyupptaget hygge i övriga riktningar.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73093-2021 artfynd.xlsx
+++ b/artfynd/A 73093-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Floraväkteri AB-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6760838</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6762359</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037246</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120977600</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037254</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113252976</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113252978</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120977598</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037081</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1822,6 +1872,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5039492</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1925,6 +1980,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113252977</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2038,6 +2098,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120977602</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2165,8 +2230,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120977601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>